--- a/docs/05b-washability-RAW-template_MN.xlsx
+++ b/docs/05b-washability-RAW-template_MN.xlsx
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +49,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -86,6 +91,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,22 +457,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="70" customHeight="1">
+    <row r="1" ht="85" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ЗААВАР: seam (давхрага) бүрийг блокоор бөглөнө. Лабын ТҮҮХИЙ дата шууд: mass_g=фракцын жин (грамм эсвэл %), ash_ad=агаар-хуурай үнс %, moisture_ad=агаар-хуурай чийг % (IM). Engine өөрөө: жинг %-д нормчилно, үнсийг d (хуурай) болгоно, NGM/cum/curve тооцоолно. Нягтын ладдерыг лабынхаа дагуу засаж болно. Дутуу мөрийг хоосон үлдээж болно.</t>
+          <t>ЗААВАР: seam бүрийг блокоор бөглө. ТҮҮХИЙ лабын дата шууд: mass_g=жин(г/%), ash_ad=агаар-хуурай үнс%, moisture_ad=чийг%(IM), vol_ad=дэгдэмхий%, sulphur_ad=хүхэр%, csn=хөөлтийн зэрэг. Engine: жинг %-д нормчилж, үнсийг хуурай болгож, NGM/cum/curve тооцоолно. Үнс/VM/Хүхэр АДДИТИВ → баяжмал дээр автоматаар тооцоолно. CSN АДДИТИВ БИШ → зөвхөн лавлагаа (лаб баталгаажуулна). Дутуу нүдийг хоосон үлдээж болно.</t>
         </is>
       </c>
     </row>
@@ -504,6 +513,21 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>moisture_ad</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>vol_ad</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>sulphur_ad</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>csn</t>
         </is>
       </c>
     </row>
@@ -527,6 +551,9 @@
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -552,6 +579,9 @@
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -577,6 +607,9 @@
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -602,6 +635,9 @@
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -627,6 +663,9 @@
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -652,6 +691,9 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -677,6 +719,9 @@
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -702,6 +747,9 @@
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -727,6 +775,9 @@
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -752,6 +803,9 @@
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -777,6 +831,9 @@
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -802,6 +859,9 @@
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -827,6 +887,9 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -852,6 +915,9 @@
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -873,6 +939,9 @@
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -898,6 +967,9 @@
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -923,6 +995,9 @@
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -948,6 +1023,9 @@
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -973,6 +1051,9 @@
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -998,6 +1079,9 @@
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1023,6 +1107,9 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1048,6 +1135,9 @@
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1073,6 +1163,9 @@
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1098,6 +1191,9 @@
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1123,6 +1219,9 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1148,6 +1247,9 @@
       <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1173,6 +1275,9 @@
       <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1198,10 +1303,13 @@
       <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
